--- a/data/trans_orig/P5706-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5706-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2007</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317168</t>
+          <t>314684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>367183</t>
+          <t>366411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>283539</t>
+          <t>280734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>334519</t>
+          <t>335175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>611697</t>
+          <t>614107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>683279</t>
+          <t>686167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203449</t>
+          <t>205262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253939</t>
+          <t>254962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212881</t>
+          <t>212212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259569</t>
+          <t>261573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426867</t>
+          <t>430398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498005</t>
+          <t>500074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89902</t>
+          <t>90991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127221</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89158</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>125618</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189318</t>
+          <t>189734</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>243415</t>
+          <t>243299</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35612</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64832</t>
+          <t>63151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>515165</t>
+          <t>515724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>576687</t>
+          <t>580035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>494396</t>
+          <t>497779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>560729</t>
+          <t>561852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1029747</t>
+          <t>1031050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1116133</t>
+          <t>1121157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238144</t>
+          <t>235597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293571</t>
+          <t>293469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239225</t>
+          <t>238719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295721</t>
+          <t>296276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489743</t>
+          <t>489105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>569572</t>
+          <t>568995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96566</t>
+          <t>94035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138904</t>
+          <t>135065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115606</t>
+          <t>116902</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162545</t>
+          <t>164258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>226405</t>
+          <t>224169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286851</t>
+          <t>283602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>40468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>69604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>392821</t>
+          <t>390472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445872</t>
+          <t>441831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>374556</t>
+          <t>375028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>423797</t>
+          <t>422367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>777752</t>
+          <t>780270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>851620</t>
+          <t>851606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154310</t>
+          <t>156236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203521</t>
+          <t>205073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151037</t>
+          <t>149579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194226</t>
+          <t>194152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319709</t>
+          <t>318282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383539</t>
+          <t>383714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47252</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76386</t>
+          <t>76751</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72378</t>
+          <t>72867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107060</t>
+          <t>107770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127146</t>
+          <t>126418</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171492</t>
+          <t>174509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57135</t>
+          <t>57193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13699</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>505202</t>
+          <t>507976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>564214</t>
+          <t>565908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>535468</t>
+          <t>536180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>598393</t>
+          <t>600765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1054545</t>
+          <t>1058121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1143318</t>
+          <t>1148105</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226764</t>
+          <t>225773</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278583</t>
+          <t>280853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261111</t>
+          <t>260917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320990</t>
+          <t>315712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>504186</t>
+          <t>502249</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>585551</t>
+          <t>583990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85295</t>
+          <t>82127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122335</t>
+          <t>120828</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>92282</t>
+          <t>93407</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>131005</t>
+          <t>130085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>185741</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241115</t>
+          <t>243951</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57428</t>
+          <t>56807</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>40838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70291</t>
+          <t>71963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78905</t>
+          <t>78338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117791</t>
+          <t>118706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23864</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37194</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1777862</t>
+          <t>1776454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1890915</t>
+          <t>1895185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1739176</t>
+          <t>1743636</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1862430</t>
+          <t>1861644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3555446</t>
+          <t>3563453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3723568</t>
+          <t>3726710</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>877421</t>
+          <t>876951</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>976983</t>
+          <t>976673</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>913740</t>
+          <t>910956</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1023439</t>
+          <t>1011572</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1811057</t>
+          <t>1811073</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1956495</t>
+          <t>1961557</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>348849</t>
+          <t>347860</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>420049</t>
+          <t>424308</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>405253</t>
+          <t>404015</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>484785</t>
+          <t>482633</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>770961</t>
+          <t>773725</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>883640</t>
+          <t>881920</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>85972</t>
+          <t>84997</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>126603</t>
+          <t>126524</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>112603</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>159073</t>
+          <t>160847</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>208347</t>
+          <t>208435</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>271662</t>
+          <t>266794</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41501</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,47 +3963,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>57725</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>43829</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>75316</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>57725</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>43424</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>75685</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2012</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>444652</t>
+          <t>444564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>497413</t>
+          <t>494744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>389674</t>
+          <t>388826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>442879</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>851552</t>
+          <t>853035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>924904</t>
+          <t>923893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139647</t>
+          <t>139796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185830</t>
+          <t>186859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177725</t>
+          <t>177174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228221</t>
+          <t>227947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>335832</t>
+          <t>335614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>402720</t>
+          <t>397843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>65882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>40201</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67950</t>
+          <t>68104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84249</t>
+          <t>84010</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123864</t>
+          <t>124458</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>20997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45667</t>
+          <t>45353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>559307</t>
+          <t>560198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>626629</t>
+          <t>627754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>551735</t>
+          <t>553339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>617238</t>
+          <t>619616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1131488</t>
+          <t>1136132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1227349</t>
+          <t>1230363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267716</t>
+          <t>270068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328508</t>
+          <t>329092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298144</t>
+          <t>297749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361805</t>
+          <t>358916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>587945</t>
+          <t>585125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>672710</t>
+          <t>668629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75934</t>
+          <t>76381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112944</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76386</t>
+          <t>74806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114328</t>
+          <t>113704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162479</t>
+          <t>158883</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>215110</t>
+          <t>213294</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31399</t>
+          <t>32246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>31793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61104</t>
+          <t>61114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,82 +5524,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2968</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>13057</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10379</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6202</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2158</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>14721</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>439323</t>
+          <t>436883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>493087</t>
+          <t>495676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>429970</t>
+          <t>430506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>488136</t>
+          <t>487804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>883903</t>
+          <t>887099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>967715</t>
+          <t>967690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168883</t>
+          <t>167573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>220151</t>
+          <t>220852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176253</t>
+          <t>174788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226138</t>
+          <t>226085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357139</t>
+          <t>361385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>432575</t>
+          <t>434683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58777</t>
+          <t>59762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94341</t>
+          <t>92596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72148</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>111097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>139956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192373</t>
+          <t>191751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>32841</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>493775</t>
+          <t>495955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555437</t>
+          <t>557722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>514859</t>
+          <t>516982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>580236</t>
+          <t>581303</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1025031</t>
+          <t>1024353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1116184</t>
+          <t>1118461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256554</t>
+          <t>254364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312151</t>
+          <t>311746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318665</t>
+          <t>318784</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>381362</t>
+          <t>378742</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>588276</t>
+          <t>588588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>673444</t>
+          <t>679644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93863</t>
+          <t>92743</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135079</t>
+          <t>133680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96812</t>
+          <t>95467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>136580</t>
+          <t>137188</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>201442</t>
+          <t>197188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>256666</t>
+          <t>255546</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29489</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55377</t>
+          <t>56319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33467</t>
+          <t>37254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1994395</t>
+          <t>1997381</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2111646</t>
+          <t>2115730</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1948165</t>
+          <t>1950047</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2070985</t>
+          <t>2070948</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3984882</t>
+          <t>3984119</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4157713</t>
+          <t>4150787</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>890946</t>
+          <t>884196</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>998885</t>
+          <t>993792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1028940</t>
+          <t>1022064</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1136313</t>
+          <t>1139047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,47 +7266,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>32,06%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1877</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2018968</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1942288</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2092746</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>28,96%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>31,98%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2018968</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1942799</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2100976</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>28,96%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>298331</t>
+          <t>297483</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>367685</t>
+          <t>368676</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>317496</t>
+          <t>316664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>391237</t>
+          <t>386106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>627451</t>
+          <t>628105</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>733211</t>
+          <t>732472</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52398</t>
+          <t>51296</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>85209</t>
+          <t>84330</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>64652</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>102483</t>
+          <t>103423</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>124283</t>
+          <t>126751</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>173369</t>
+          <t>182039</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>44590</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38582</t>
+          <t>37405</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>69551</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2016</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>281076</t>
+          <t>282214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>334232</t>
+          <t>333957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>266747</t>
+          <t>268687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318872</t>
+          <t>318661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>562830</t>
+          <t>563139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>638042</t>
+          <t>632865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221173</t>
+          <t>219592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270148</t>
+          <t>267706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213643</t>
+          <t>214503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262437</t>
+          <t>263775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448128</t>
+          <t>448486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516227</t>
+          <t>516031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83283</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122898</t>
+          <t>120406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98712</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136826</t>
+          <t>139573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>191151</t>
+          <t>194392</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245705</t>
+          <t>250602</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46880</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>494890</t>
+          <t>496785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>559595</t>
+          <t>561561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>498154</t>
+          <t>496809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>563676</t>
+          <t>564221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1013060</t>
+          <t>1008462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1107106</t>
+          <t>1103703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320867</t>
+          <t>321746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>383832</t>
+          <t>381858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321703</t>
+          <t>319353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381347</t>
+          <t>382884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659775</t>
+          <t>662147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>746757</t>
+          <t>747779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142366</t>
+          <t>144801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110862</t>
+          <t>108817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158290</t>
+          <t>154087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>223063</t>
+          <t>222470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286254</t>
+          <t>281968</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>31235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57848</t>
+          <t>58168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,47 +9166,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10812</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>11341</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288756</t>
+          <t>290097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>345426</t>
+          <t>344944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>286647</t>
+          <t>289422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>344618</t>
+          <t>345273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>593001</t>
+          <t>586159</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>673213</t>
+          <t>672151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258531</t>
+          <t>257859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314730</t>
+          <t>312165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>281077</t>
+          <t>279744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>339195</t>
+          <t>335118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>552613</t>
+          <t>552401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>634956</t>
+          <t>631912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117033</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160177</t>
+          <t>160367</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124719</t>
+          <t>121524</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168866</t>
+          <t>169408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>250511</t>
+          <t>252553</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>312634</t>
+          <t>317939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41026</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>480930</t>
+          <t>482268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>541103</t>
+          <t>544001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>541502</t>
+          <t>541284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>609961</t>
+          <t>609040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1041623</t>
+          <t>1048076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1134233</t>
+          <t>1134136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253935</t>
+          <t>250425</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312969</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283843</t>
+          <t>284403</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>343581</t>
+          <t>345588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>553019</t>
+          <t>550069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>636422</t>
+          <t>633413</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91492</t>
+          <t>91948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132051</t>
+          <t>130700</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93306</t>
+          <t>91790</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135032</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>196480</t>
+          <t>194886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>253333</t>
+          <t>251539</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37627</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46127</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74894</t>
+          <t>73288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1603173</t>
+          <t>1597188</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1719519</t>
+          <t>1724275</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1654408</t>
+          <t>1658512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1771173</t>
+          <t>1778527</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3295616</t>
+          <t>3294940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3468055</t>
+          <t>3461790</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1116840</t>
+          <t>1110418</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1220990</t>
+          <t>1222768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1152114</t>
+          <t>1137320</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1268690</t>
+          <t>1259032</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2292649</t>
+          <t>2291060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2454564</t>
+          <t>2451131</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>429112</t>
+          <t>423695</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514418</t>
+          <t>512545</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>464537</t>
+          <t>469570</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>552490</t>
+          <t>554000</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>923105</t>
+          <t>918919</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1036062</t>
+          <t>1037138</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>54483</t>
+          <t>55689</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91119</t>
+          <t>89756</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71950</t>
+          <t>71083</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>110619</t>
+          <t>109032</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>136826</t>
+          <t>134471</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>189320</t>
+          <t>186972</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>50496</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2023</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>350635</t>
+          <t>351835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>402873</t>
+          <t>403581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353185</t>
+          <t>350532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>395376</t>
+          <t>392447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>716970</t>
+          <t>715230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>784949</t>
+          <t>784059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149114</t>
+          <t>148523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193438</t>
+          <t>194308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>183217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216749</t>
+          <t>218875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340647</t>
+          <t>340065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>395917</t>
+          <t>397751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72168</t>
+          <t>71120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76711</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>104531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>139537</t>
+          <t>138212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29822</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>38146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38812</t>
+          <t>38250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61763</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>24581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>671871</t>
+          <t>672331</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>965557</t>
+          <t>988271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>478268</t>
+          <t>479716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>533314</t>
+          <t>532624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1176896</t>
+          <t>1171000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1586995</t>
+          <t>1604065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160796</t>
+          <t>147550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380079</t>
+          <t>383780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289984</t>
+          <t>292969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340766</t>
+          <t>341427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>402128</t>
+          <t>400636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701364</t>
+          <t>702941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>38699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98417</t>
+          <t>100077</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65584</t>
+          <t>65405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>92541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94238</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>177842</t>
+          <t>180690</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>54947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48301</t>
+          <t>46333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90987</t>
+          <t>88441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>32760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>360993</t>
+          <t>359243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>422374</t>
+          <t>420749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>231589</t>
+          <t>193042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>564078</t>
+          <t>561232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>554060</t>
+          <t>527628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>957568</t>
+          <t>954507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201529</t>
+          <t>201722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257422</t>
+          <t>260779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>273628</t>
+          <t>274628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>659193</t>
+          <t>703981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>498391</t>
+          <t>500603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>971404</t>
+          <t>1008512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47310</t>
+          <t>48648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81751</t>
+          <t>83033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72177</t>
+          <t>71991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>78354</t>
+          <t>76408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143775</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29537</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20972</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47016</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>530322</t>
+          <t>531670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>588719</t>
+          <t>591303</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>658294</t>
+          <t>658019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>779614</t>
+          <t>769335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1207305</t>
+          <t>1208999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1341281</t>
+          <t>1346036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223310</t>
+          <t>222159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272467</t>
+          <t>272805</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202533</t>
+          <t>209615</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289058</t>
+          <t>289436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>451222</t>
+          <t>450117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>548720</t>
+          <t>547312</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52355</t>
+          <t>52201</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82372</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63506</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95881</t>
+          <t>97760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>124656</t>
+          <t>125574</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170095</t>
+          <t>171675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>50359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29244</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61691</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96055</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1992979</t>
+          <t>1999035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2393436</t>
+          <t>2403588</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1651425</t>
+          <t>1588308</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2151091</t>
+          <t>2144836</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3804072</t>
+          <t>3788568</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4410046</t>
+          <t>4384281</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>739558</t>
+          <t>736165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1032435</t>
+          <t>1030005</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1033815</t>
+          <t>1040866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1615130</t>
+          <t>1707779</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1915899</t>
+          <t>1939360</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2627615</t>
+          <t>2620171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>202785</t>
+          <t>196707</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>294566</t>
+          <t>296144</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>229043</t>
+          <t>219704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>310462</t>
+          <t>307463</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>459744</t>
+          <t>462057</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>590247</t>
+          <t>585319</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73929</t>
+          <t>74888</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>121630</t>
+          <t>119831</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>107070</t>
+          <t>104831</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>153100</t>
+          <t>154869</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>192264</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>259711</t>
+          <t>264311</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>53552</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,47 +14854,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>37759</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>28675</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>52794</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>37759</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>28122</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>51859</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>60686</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>94928</t>
+          <t>95009</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/P5706-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5706-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>314684</t>
+          <t>312586</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>366411</t>
+          <t>365246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280734</t>
+          <t>284131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>335175</t>
+          <t>333358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>614107</t>
+          <t>610450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>686167</t>
+          <t>682455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205262</t>
+          <t>204901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254962</t>
+          <t>255608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212212</t>
+          <t>211460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261573</t>
+          <t>259830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>430398</t>
+          <t>430499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>500074</t>
+          <t>498116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90991</t>
+          <t>91538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129014</t>
+          <t>129765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,49 +974,49 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>106669</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>89373</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>127957</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>18,59%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>106669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>87410</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>125618</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>216</t>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189734</t>
+          <t>191406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>243299</t>
+          <t>242517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34573</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63151</t>
+          <t>65021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>515724</t>
+          <t>516018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>580035</t>
+          <t>577893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>497779</t>
+          <t>497068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>561852</t>
+          <t>557867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1031050</t>
+          <t>1032516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1121157</t>
+          <t>1120993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>235597</t>
+          <t>237827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293469</t>
+          <t>293411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238719</t>
+          <t>239336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296276</t>
+          <t>294046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489105</t>
+          <t>492574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>568995</t>
+          <t>570615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94035</t>
+          <t>94270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135065</t>
+          <t>136411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116902</t>
+          <t>117635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164258</t>
+          <t>161555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224169</t>
+          <t>226127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283602</t>
+          <t>287299</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>39038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69604</t>
+          <t>68737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390472</t>
+          <t>390007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>441831</t>
+          <t>443613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>375028</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>422367</t>
+          <t>421858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>780270</t>
+          <t>774820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>851606</t>
+          <t>848038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156236</t>
+          <t>158436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205073</t>
+          <t>203677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149579</t>
+          <t>148435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194152</t>
+          <t>190964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>318282</t>
+          <t>321023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383714</t>
+          <t>384704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76751</t>
+          <t>78486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72867</t>
+          <t>73268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107770</t>
+          <t>107022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126418</t>
+          <t>128390</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174509</t>
+          <t>171084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>36660</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57193</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>507976</t>
+          <t>501744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>565908</t>
+          <t>562677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>536180</t>
+          <t>534352</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>600765</t>
+          <t>597820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1058121</t>
+          <t>1058766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1148105</t>
+          <t>1147665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225773</t>
+          <t>225349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280853</t>
+          <t>279486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>260917</t>
+          <t>263078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315712</t>
+          <t>322147</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>502249</t>
+          <t>499466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583990</t>
+          <t>583135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82127</t>
+          <t>84517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120828</t>
+          <t>121360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>90768</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>130085</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>189541</t>
+          <t>186320</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243951</t>
+          <t>240120</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56807</t>
+          <t>57189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71963</t>
+          <t>69102</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78338</t>
+          <t>78339</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118706</t>
+          <t>117410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1776454</t>
+          <t>1782455</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1895185</t>
+          <t>1895660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1743636</t>
+          <t>1753313</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1861644</t>
+          <t>1860341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3563453</t>
+          <t>3557998</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3726710</t>
+          <t>3729954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>876951</t>
+          <t>871802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>976673</t>
+          <t>978859</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>910956</t>
+          <t>905533</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1011572</t>
+          <t>1015005</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1811073</t>
+          <t>1811345</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1961557</t>
+          <t>1956761</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>348783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>424308</t>
+          <t>422390</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>404015</t>
+          <t>407884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>482633</t>
+          <t>486332</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>773725</t>
+          <t>770266</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>881920</t>
+          <t>886079</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>84750</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>126524</t>
+          <t>124773</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111628</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>160847</t>
+          <t>160810</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>208435</t>
+          <t>207899</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>266794</t>
+          <t>269583</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45136</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43829</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>74534</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>444564</t>
+          <t>445618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>494744</t>
+          <t>498114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388826</t>
+          <t>389104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>442473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>853035</t>
+          <t>846853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>923893</t>
+          <t>923375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139796</t>
+          <t>141141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186859</t>
+          <t>187206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177174</t>
+          <t>177604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227947</t>
+          <t>229180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>335614</t>
+          <t>335884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>397843</t>
+          <t>404012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65882</t>
+          <t>65091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68104</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84010</t>
+          <t>85185</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124458</t>
+          <t>126517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45353</t>
+          <t>45415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>560198</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>627754</t>
+          <t>627578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>553339</t>
+          <t>553573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>619616</t>
+          <t>620426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1136132</t>
+          <t>1130728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1230363</t>
+          <t>1223908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270068</t>
+          <t>267300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329092</t>
+          <t>328221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297749</t>
+          <t>296641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>358916</t>
+          <t>360177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585125</t>
+          <t>583661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>668629</t>
+          <t>671842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76381</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114541</t>
+          <t>114535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>74625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113704</t>
+          <t>111737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>158883</t>
+          <t>159954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>213294</t>
+          <t>212191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37447</t>
+          <t>37523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61114</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5509,62 +5509,62 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2968</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8848</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11332</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9664</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>436883</t>
+          <t>436201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>495676</t>
+          <t>493840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>430506</t>
+          <t>432995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>487804</t>
+          <t>488833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887099</t>
+          <t>887214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>967690</t>
+          <t>966789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167573</t>
+          <t>167251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>220852</t>
+          <t>221859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174788</t>
+          <t>176261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226085</t>
+          <t>225475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>361385</t>
+          <t>359853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434683</t>
+          <t>430381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59762</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92596</t>
+          <t>96637</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>72269</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111097</t>
+          <t>107995</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139956</t>
+          <t>142220</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>191751</t>
+          <t>192379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>21055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45802</t>
+          <t>45998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>25984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>495955</t>
+          <t>492381</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>557722</t>
+          <t>557880</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>516982</t>
+          <t>510787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>581303</t>
+          <t>578512</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1024353</t>
+          <t>1030487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1118461</t>
+          <t>1122167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254364</t>
+          <t>253577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311746</t>
+          <t>310359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318784</t>
+          <t>319889</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378742</t>
+          <t>379664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>588588</t>
+          <t>586658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>679644</t>
+          <t>672537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92743</t>
+          <t>91820</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>133680</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95467</t>
+          <t>96178</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>137188</t>
+          <t>135527</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>197188</t>
+          <t>197813</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>255546</t>
+          <t>253305</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35184</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56319</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>34764</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1997381</t>
+          <t>2000856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2115730</t>
+          <t>2123399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1950047</t>
+          <t>1954000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2070948</t>
+          <t>2071952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3984119</t>
+          <t>3978551</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4150787</t>
+          <t>4147049</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>884196</t>
+          <t>885604</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>993792</t>
+          <t>994461</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1022064</t>
+          <t>1016955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1139047</t>
+          <t>1130374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1942288</t>
+          <t>1945202</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2092746</t>
+          <t>2095607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>297483</t>
+          <t>297250</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>368676</t>
+          <t>368396</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>316664</t>
+          <t>311591</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>386106</t>
+          <t>388561</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>628105</t>
+          <t>628890</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>732472</t>
+          <t>730908</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>51296</t>
+          <t>51376</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>84330</t>
+          <t>85061</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>103423</t>
+          <t>102606</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>126751</t>
+          <t>127656</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>182039</t>
+          <t>177426</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44590</t>
+          <t>43380</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>38352</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>69551</t>
+          <t>71249</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282214</t>
+          <t>280215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333957</t>
+          <t>333466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268687</t>
+          <t>268404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318661</t>
+          <t>319207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,47 +8067,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>47,58%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>600396</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>563644</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>638728</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>41,92%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>47,5%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>600396</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>563139</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>632865</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>44,65%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>41,88%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>219592</t>
+          <t>218400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267706</t>
+          <t>270943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214503</t>
+          <t>212074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263775</t>
+          <t>259001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448486</t>
+          <t>445951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516031</t>
+          <t>518164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>83510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120406</t>
+          <t>123848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139573</t>
+          <t>141989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>194392</t>
+          <t>192409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250602</t>
+          <t>248154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>27829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>46876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>496785</t>
+          <t>496520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>561561</t>
+          <t>562504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>496809</t>
+          <t>499097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>564221</t>
+          <t>565988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1008462</t>
+          <t>1012013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1103703</t>
+          <t>1104088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321746</t>
+          <t>321398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381858</t>
+          <t>384295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319353</t>
+          <t>318721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382884</t>
+          <t>383964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662147</t>
+          <t>653076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>747779</t>
+          <t>744594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101774</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144801</t>
+          <t>142961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108817</t>
+          <t>109942</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154087</t>
+          <t>155894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222470</t>
+          <t>225538</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>281968</t>
+          <t>285841</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31235</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>58907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>290097</t>
+          <t>287749</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>344944</t>
+          <t>343578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289422</t>
+          <t>286185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>345273</t>
+          <t>342300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>586159</t>
+          <t>593454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>672151</t>
+          <t>674065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257859</t>
+          <t>259252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>312165</t>
+          <t>312981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>279744</t>
+          <t>280594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>335118</t>
+          <t>335631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>552401</t>
+          <t>552520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>631912</t>
+          <t>632347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118563</t>
+          <t>116394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160367</t>
+          <t>161499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121524</t>
+          <t>122535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>169408</t>
+          <t>168567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252553</t>
+          <t>252067</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>317939</t>
+          <t>314379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>482268</t>
+          <t>478000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>544001</t>
+          <t>538929</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>541284</t>
+          <t>544469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>609040</t>
+          <t>609553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1048076</t>
+          <t>1041243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1134136</t>
+          <t>1133627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250425</t>
+          <t>254815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>309257</t>
+          <t>312848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>284403</t>
+          <t>284099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345588</t>
+          <t>344513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>550069</t>
+          <t>553980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>633413</t>
+          <t>636934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91948</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130700</t>
+          <t>130616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91790</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135681</t>
+          <t>134944</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>194886</t>
+          <t>196461</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>251539</t>
+          <t>255690</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>36416</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44071</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73288</t>
+          <t>74269</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1597188</t>
+          <t>1606991</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1724275</t>
+          <t>1722734</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1658512</t>
+          <t>1653769</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1778527</t>
+          <t>1772420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3294940</t>
+          <t>3296750</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3461790</t>
+          <t>3465424</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1110418</t>
+          <t>1109523</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1222768</t>
+          <t>1223596</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1137320</t>
+          <t>1154810</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1259032</t>
+          <t>1273161</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2291060</t>
+          <t>2289253</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2451131</t>
+          <t>2450265</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>423695</t>
+          <t>427771</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>512545</t>
+          <t>506841</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>469570</t>
+          <t>468788</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>554000</t>
+          <t>552829</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>918919</t>
+          <t>921055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1037138</t>
+          <t>1038319</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55689</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>89756</t>
+          <t>91866</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71083</t>
+          <t>71777</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>109032</t>
+          <t>109430</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>134471</t>
+          <t>135999</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>186972</t>
+          <t>189816</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>28160</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>51065</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>377490</t>
+          <t>398950</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351835</t>
+          <t>370613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>403581</t>
+          <t>426353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>373027</t>
+          <t>403337</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>350532</t>
+          <t>380214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>392447</t>
+          <t>424653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>750516</t>
+          <t>802287</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>715230</t>
+          <t>767596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>784059</t>
+          <t>835155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>170128</t>
+          <t>192014</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148523</t>
+          <t>168572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194308</t>
+          <t>217431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>198521</t>
+          <t>216171</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183217</t>
+          <t>196996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218875</t>
+          <t>235612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>368649</t>
+          <t>408185</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340065</t>
+          <t>377936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>397751</t>
+          <t>439269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56150</t>
+          <t>63366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44896</t>
+          <t>48956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71120</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64280</t>
+          <t>69203</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>82730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>120430</t>
+          <t>132569</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104531</t>
+          <t>115347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>138212</t>
+          <t>154376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29329</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>32672</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38146</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>54352</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>41689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62015</t>
+          <t>67809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>633314</t>
+          <t>688283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>633314</t>
+          <t>688283</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633314</t>
+          <t>688283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>671669</t>
+          <t>728779</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>671669</t>
+          <t>728779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>671669</t>
+          <t>728779</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1304983</t>
+          <t>1417062</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1304983</t>
+          <t>1417062</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1304983</t>
+          <t>1417062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>788451</t>
+          <t>585916</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>672331</t>
+          <t>551126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>988271</t>
+          <t>623110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>505897</t>
+          <t>552063</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>479716</t>
+          <t>522160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>532624</t>
+          <t>580890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1294346</t>
+          <t>1137979</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1171000</t>
+          <t>1095671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1604065</t>
+          <t>1185807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>293953</t>
+          <t>330386</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147550</t>
+          <t>296718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>383780</t>
+          <t>360269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>316737</t>
+          <t>363604</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292969</t>
+          <t>336000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341427</t>
+          <t>390773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>610690</t>
+          <t>693990</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>400636</t>
+          <t>651407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>702941</t>
+          <t>734486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71445</t>
+          <t>83658</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38699</t>
+          <t>66741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100077</t>
+          <t>108732</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,27 +12597,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78358</t>
+          <t>88862</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65405</t>
+          <t>74724</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92541</t>
+          <t>103405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>149803</t>
+          <t>172520</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98363</t>
+          <t>149530</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180690</t>
+          <t>199231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28668</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42510</t>
+          <t>51108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42387</t>
+          <t>48776</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54947</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71055</t>
+          <t>86697</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46333</t>
+          <t>68716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88441</t>
+          <t>104812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>36251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1191293</t>
+          <t>1047252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1191293</t>
+          <t>1047252</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1191293</t>
+          <t>1047252</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956172</t>
+          <t>1067858</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956172</t>
+          <t>1067858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956172</t>
+          <t>1067858</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2147464</t>
+          <t>2115110</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2147464</t>
+          <t>2115110</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2147464</t>
+          <t>2115110</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>391404</t>
+          <t>430532</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>359243</t>
+          <t>397806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>420749</t>
+          <t>461454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>428261</t>
+          <t>465108</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193042</t>
+          <t>439092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>561232</t>
+          <t>490682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>819665</t>
+          <t>895639</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>527628</t>
+          <t>856062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>954507</t>
+          <t>934869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>266856</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201722</t>
+          <t>238991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>260779</t>
+          <t>300986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>427953</t>
+          <t>254527</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>274628</t>
+          <t>229925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703981</t>
+          <t>277792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>656986</t>
+          <t>521382</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>500603</t>
+          <t>485009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1008512</t>
+          <t>559164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63202</t>
+          <t>75782</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48648</t>
+          <t>58061</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83033</t>
+          <t>99738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>61692</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>50296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71991</t>
+          <t>79048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>114836</t>
+          <t>137474</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76408</t>
+          <t>114964</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143709</t>
+          <t>163610</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>29343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>41933</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>31662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>56299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>702771</t>
+          <t>800055</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>702771</t>
+          <t>800055</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>702771</t>
+          <t>800055</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>932620</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>932620</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>932620</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1635391</t>
+          <t>1611591</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1635391</t>
+          <t>1611591</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1635391</t>
+          <t>1611591</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>561222</t>
+          <t>590029</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>531670</t>
+          <t>558193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>591303</t>
+          <t>625339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>696294</t>
+          <t>672149</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>658019</t>
+          <t>644204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>769335</t>
+          <t>702886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1257516</t>
+          <t>1262178</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1208999</t>
+          <t>1221825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1346036</t>
+          <t>1307760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>245906</t>
+          <t>269333</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222159</t>
+          <t>238751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272805</t>
+          <t>297426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>260178</t>
+          <t>289128</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>209615</t>
+          <t>260843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289436</t>
+          <t>312829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>506085</t>
+          <t>558462</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>450117</t>
+          <t>518427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>547312</t>
+          <t>593304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>71834</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52201</t>
+          <t>56980</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82938</t>
+          <t>88296</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>80969</t>
+          <t>88886</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>75215</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97760</t>
+          <t>104442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>147104</t>
+          <t>160720</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125574</t>
+          <t>140013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>183507</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35602</t>
+          <t>38907</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52447</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>75528</t>
+          <t>85880</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60898</t>
+          <t>70753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94088</t>
+          <t>104530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -14152,102 +14152,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>16942</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>10744</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>24802</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>34148</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>24721</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>46911</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>12781</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>19375</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>27841</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>19862</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>38744</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>923925</t>
+          <t>987308</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>923925</t>
+          <t>987308</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>923925</t>
+          <t>987308</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1090148</t>
+          <t>1114079</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1090148</t>
+          <t>1114079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1090148</t>
+          <t>1114079</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2014074</t>
+          <t>2101387</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2014074</t>
+          <t>2101387</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2014074</t>
+          <t>2101387</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2118566</t>
+          <t>2005426</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1999035</t>
+          <t>1937776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2403588</t>
+          <t>2066020</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2003477</t>
+          <t>2092657</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1588308</t>
+          <t>2032911</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2144836</t>
+          <t>2146540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4122043</t>
+          <t>4098083</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3788568</t>
+          <t>4009455</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4384281</t>
+          <t>4181046</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>939020</t>
+          <t>1058589</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>736165</t>
+          <t>1003833</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1030005</t>
+          <t>1117695</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1203390</t>
+          <t>1123429</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1040866</t>
+          <t>1070331</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1707779</t>
+          <t>1173254</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2142410</t>
+          <t>2182019</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1939360</t>
+          <t>2108355</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2620171</t>
+          <t>2261378</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>256932</t>
+          <t>294639</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>196707</t>
+          <t>259907</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>296144</t>
+          <t>331898</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>275241</t>
+          <t>308643</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>219704</t>
+          <t>279428</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>307463</t>
+          <t>340567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>532173</t>
+          <t>603283</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>462057</t>
+          <t>557598</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>585319</t>
+          <t>651615</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>97833</t>
+          <t>120050</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74888</t>
+          <t>100193</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119831</t>
+          <t>143868</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>130741</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>104831</t>
+          <t>129497</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>154869</t>
+          <t>171376</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>228574</t>
+          <t>268861</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>195270</t>
+          <t>239975</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>264311</t>
+          <t>299897</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>44192</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>61616</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>37759</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52794</t>
+          <t>64309</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>76712</t>
+          <t>92904</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59707</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>95009</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3451303</t>
+          <t>3522897</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3451303</t>
+          <t>3522897</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3451303</t>
+          <t>3522897</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3650609</t>
+          <t>3722252</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3650609</t>
+          <t>3722252</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3650609</t>
+          <t>3722252</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7101912</t>
+          <t>7245149</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7101912</t>
+          <t>7245149</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7101912</t>
+          <t>7245149</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
